--- a/examples/example_output/scores.xlsx
+++ b/examples/example_output/scores.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="G2">
-        <v>0.03622054308652878</v>
+        <v>0.03622051700949669</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -517,7 +517,7 @@
         <v>6</v>
       </c>
       <c r="G3">
-        <v>0.02158412896096706</v>
+        <v>0.02158414572477341</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="G6">
-        <v>0.04116277396678925</v>
+        <v>0.04116276279091835</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>18</v>
       </c>
       <c r="G7">
-        <v>0.02538027986884117</v>
+        <v>0.02538025565445423</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -647,7 +647,7 @@
         <v>21</v>
       </c>
       <c r="G8">
-        <v>0.006461409851908684</v>
+        <v>0.006461403798311949</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -673,7 +673,7 @@
         <v>24</v>
       </c>
       <c r="G9">
-        <v>0.04659212380647659</v>
+        <v>0.04659212008118629</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -699,7 +699,7 @@
         <v>27</v>
       </c>
       <c r="G10">
-        <v>0.05809244140982628</v>
+        <v>0.05809248611330986</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -725,7 +725,7 @@
         <v>30</v>
       </c>
       <c r="G11">
-        <v>0.03862911090254784</v>
+        <v>0.03862906619906425</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -777,7 +777,7 @@
         <v>36</v>
       </c>
       <c r="G13">
-        <v>0.01764045841991901</v>
+        <v>0.01764046587049961</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>39</v>
       </c>
       <c r="G14">
-        <v>0.02214250527322292</v>
+        <v>0.02214252576231956</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -829,7 +829,7 @@
         <v>42</v>
       </c>
       <c r="G15">
-        <v>0.02388827875256538</v>
+        <v>0.02388823963701725</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -881,7 +881,7 @@
         <v>48</v>
       </c>
       <c r="G17">
-        <v>0.0195439588278532</v>
+        <v>0.01954395137727261</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>51</v>
       </c>
       <c r="G18">
-        <v>0.02676285989582539</v>
+        <v>0.02676287293434143</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -933,7 +933,7 @@
         <v>54</v>
       </c>
       <c r="G19">
-        <v>0.02359981462359428</v>
+        <v>0.02359982579946518</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>60</v>
       </c>
       <c r="G21">
-        <v>0.03216664493083954</v>
+        <v>0.03216662630438805</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1011,7 +1011,7 @@
         <v>63</v>
       </c>
       <c r="G22">
-        <v>0.05849415808916092</v>
+        <v>0.05849422886967659</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1037,7 +1037,7 @@
         <v>66</v>
       </c>
       <c r="G23">
-        <v>0.03604817390441895</v>
+        <v>0.03604815900325775</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1063,7 +1063,7 @@
         <v>69</v>
       </c>
       <c r="G24">
-        <v>0.02336918562650681</v>
+        <v>0.02336918003857136</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1089,7 +1089,7 @@
         <v>72</v>
       </c>
       <c r="G25">
-        <v>0.05253926664590836</v>
+        <v>0.05253930389881134</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>75</v>
       </c>
       <c r="G26">
-        <v>0.05579833313822746</v>
+        <v>0.05579842254519463</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -1141,7 +1141,7 @@
         <v>78</v>
       </c>
       <c r="G27">
-        <v>0.05765799805521965</v>
+        <v>0.05765801295638084</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -1167,7 +1167,7 @@
         <v>81</v>
       </c>
       <c r="G28">
-        <v>0.01717087440192699</v>
+        <v>0.01717088185250759</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>87</v>
       </c>
       <c r="G30">
-        <v>0.01853477954864502</v>
+        <v>0.01853478513658047</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>93</v>
       </c>
       <c r="G32">
-        <v>0.01122466009110212</v>
+        <v>0.01122466567903757</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>96</v>
       </c>
       <c r="G33">
-        <v>0.02369412779808044</v>
+        <v>0.02369414456188679</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>99</v>
       </c>
       <c r="G34">
-        <v>0.0491204597055912</v>
+        <v>0.0491204708814621</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         <v>105</v>
       </c>
       <c r="G36">
-        <v>0.06072993576526642</v>
+        <v>0.06072994694113731</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -1401,7 +1401,7 @@
         <v>108</v>
       </c>
       <c r="G37">
-        <v>0.04660471528768539</v>
+        <v>0.04660475999116898</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -1427,7 +1427,7 @@
         <v>111</v>
       </c>
       <c r="G38">
-        <v>0.0529206320643425</v>
+        <v>0.05292065814137459</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -1479,7 +1479,7 @@
         <v>117</v>
       </c>
       <c r="G40">
-        <v>0.0323476754128933</v>
+        <v>0.0323476679623127</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>123</v>
       </c>
       <c r="G42">
-        <v>0.02780932746827602</v>
+        <v>0.02780933491885662</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>126</v>
       </c>
       <c r="G43">
-        <v>0.03148753941059113</v>
+        <v>0.03148755431175232</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -1583,7 +1583,7 @@
         <v>129</v>
       </c>
       <c r="G44">
-        <v>0.006968164350837469</v>
+        <v>0.006968157831579447</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -1609,7 +1609,7 @@
         <v>132</v>
       </c>
       <c r="G45">
-        <v>0.01812420785427094</v>
+        <v>0.01812419109046459</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -1661,7 +1661,7 @@
         <v>138</v>
       </c>
       <c r="G47">
-        <v>0.01219927612692118</v>
+        <v>0.01219927053898573</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>141</v>
       </c>
       <c r="G48">
-        <v>0.008585693314671516</v>
+        <v>0.008585684932768345</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -1765,7 +1765,7 @@
         <v>150</v>
       </c>
       <c r="G51">
-        <v>0.01518532726913691</v>
+        <v>0.01518533378839493</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>153</v>
       </c>
       <c r="G52">
-        <v>0.007989184930920601</v>
+        <v>0.007989181205630302</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>156</v>
       </c>
       <c r="G53">
-        <v>0.02858107537031174</v>
+        <v>0.02858109027147293</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -1843,7 +1843,7 @@
         <v>159</v>
       </c>
       <c r="G54">
-        <v>0.01431059651076794</v>
+        <v>0.0143105760216713</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -1869,7 +1869,7 @@
         <v>162</v>
       </c>
       <c r="G55">
-        <v>0.02222609519958496</v>
+        <v>0.02222610451281071</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -1895,7 +1895,7 @@
         <v>165</v>
       </c>
       <c r="G56">
-        <v>0.009088635444641113</v>
+        <v>0.00908863078802824</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -1947,7 +1947,7 @@
         <v>171</v>
       </c>
       <c r="G58">
-        <v>0.01769732870161533</v>
+        <v>0.01769734732806683</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -1973,7 +1973,7 @@
         <v>174</v>
       </c>
       <c r="G59">
-        <v>0.009347284212708473</v>
+        <v>0.009347271174192429</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -1999,7 +1999,7 @@
         <v>177</v>
       </c>
       <c r="G60">
-        <v>0.008000778034329414</v>
+        <v>0.008000762201845646</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -2025,7 +2025,7 @@
         <v>180</v>
       </c>
       <c r="G61">
-        <v>0.01040696538984776</v>
+        <v>0.01040698029100895</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>183</v>
       </c>
       <c r="G62">
-        <v>0.01898893527686596</v>
+        <v>0.01898894459009171</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -2077,7 +2077,7 @@
         <v>186</v>
       </c>
       <c r="G63">
-        <v>0.006930519361048937</v>
+        <v>0.006930516101419926</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -2103,7 +2103,7 @@
         <v>189</v>
       </c>
       <c r="G64">
-        <v>0.01302307192236185</v>
+        <v>0.01302307844161987</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -2129,7 +2129,7 @@
         <v>192</v>
       </c>
       <c r="G65">
-        <v>0.01785731129348278</v>
+        <v>0.01785730384290218</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -2155,7 +2155,7 @@
         <v>195</v>
       </c>
       <c r="G66">
-        <v>0.04025552794337273</v>
+        <v>0.04025551676750183</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2181,7 +2181,7 @@
         <v>198</v>
       </c>
       <c r="G67">
-        <v>0.01420970261096954</v>
+        <v>0.0142096895724535</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2207,7 +2207,7 @@
         <v>201</v>
       </c>
       <c r="G68">
-        <v>0.01011133845895529</v>
+        <v>0.01011133380234241</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -2233,7 +2233,7 @@
         <v>204</v>
       </c>
       <c r="G69">
-        <v>0.02499415911734104</v>
+        <v>0.02499419637024403</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>207</v>
       </c>
       <c r="G70">
-        <v>0.009452689439058304</v>
+        <v>0.009452680125832558</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -2285,7 +2285,7 @@
         <v>210</v>
       </c>
       <c r="G71">
-        <v>0.007262127473950386</v>
+        <v>0.007262120489031076</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>213</v>
       </c>
       <c r="G72">
-        <v>0.009809084236621857</v>
+        <v>0.009809079580008984</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -2363,7 +2363,7 @@
         <v>219</v>
       </c>
       <c r="G74">
-        <v>0.01563013717532158</v>
+        <v>0.01563015207648277</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -2389,7 +2389,7 @@
         <v>222</v>
       </c>
       <c r="G75">
-        <v>0.01100278180092573</v>
+        <v>0.01100278086960316</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -2415,7 +2415,7 @@
         <v>225</v>
       </c>
       <c r="G76">
-        <v>0.01225402858108282</v>
+        <v>0.01225402392446995</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -2467,7 +2467,7 @@
         <v>231</v>
       </c>
       <c r="G78">
-        <v>0.0133262574672699</v>
+        <v>0.01332624442875385</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -2493,7 +2493,7 @@
         <v>234</v>
       </c>
       <c r="G79">
-        <v>0.01086451485753059</v>
+        <v>0.01086451020091772</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -2519,7 +2519,7 @@
         <v>237</v>
       </c>
       <c r="G80">
-        <v>0.01299538090825081</v>
+        <v>0.01299537438899279</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -2545,7 +2545,7 @@
         <v>240</v>
       </c>
       <c r="G81">
-        <v>0.04246038571000099</v>
+        <v>0.04246041551232338</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -2597,7 +2597,7 @@
         <v>246</v>
       </c>
       <c r="G83">
-        <v>0.007137286476790905</v>
+        <v>0.007137283217161894</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -2623,7 +2623,7 @@
         <v>249</v>
       </c>
       <c r="G84">
-        <v>0.009048915468156338</v>
+        <v>0.009048911742866039</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -2649,7 +2649,7 @@
         <v>252</v>
       </c>
       <c r="G85">
-        <v>0.01710559986531734</v>
+        <v>0.01710561476647854</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -2675,7 +2675,7 @@
         <v>255</v>
       </c>
       <c r="G86">
-        <v>0.01074209157377481</v>
+        <v>0.01074209064245224</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -2701,7 +2701,7 @@
         <v>258</v>
       </c>
       <c r="G87">
-        <v>0.01328424550592899</v>
+        <v>0.01328423898667097</v>
       </c>
       <c r="H87">
         <v>1</v>
@@ -2727,7 +2727,7 @@
         <v>261</v>
       </c>
       <c r="G88">
-        <v>0.003429010743275285</v>
+        <v>0.003429017262533307</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>264</v>
       </c>
       <c r="G89">
-        <v>0.007975010201334953</v>
+        <v>0.007975022308528423</v>
       </c>
       <c r="H89">
         <v>1</v>
@@ -2779,7 +2779,7 @@
         <v>267</v>
       </c>
       <c r="G90">
-        <v>0.01389855705201626</v>
+        <v>0.0138985700905323</v>
       </c>
       <c r="H90">
         <v>1</v>
@@ -2805,7 +2805,7 @@
         <v>270</v>
       </c>
       <c r="G91">
-        <v>0.01221018470823765</v>
+        <v>0.01221017353236675</v>
       </c>
       <c r="H91">
         <v>1</v>
@@ -2831,7 +2831,7 @@
         <v>273</v>
       </c>
       <c r="G92">
-        <v>0.01980655826628208</v>
+        <v>0.01980657689273357</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -2857,7 +2857,7 @@
         <v>276</v>
       </c>
       <c r="G93">
-        <v>0.01391581725329161</v>
+        <v>0.01391581818461418</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -2883,7 +2883,7 @@
         <v>279</v>
       </c>
       <c r="G94">
-        <v>0.009487021714448929</v>
+        <v>0.009487004019320011</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -2909,7 +2909,7 @@
         <v>282</v>
       </c>
       <c r="G95">
-        <v>0.005738787353038788</v>
+        <v>0.005738792475312948</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -2935,7 +2935,7 @@
         <v>285</v>
       </c>
       <c r="G96">
-        <v>0.01413447596132755</v>
+        <v>0.01413446944206953</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -2961,7 +2961,7 @@
         <v>288</v>
       </c>
       <c r="G97">
-        <v>0.01282060984522104</v>
+        <v>0.01282060332596302</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -2987,7 +2987,7 @@
         <v>291</v>
       </c>
       <c r="G98">
-        <v>0.007882542908191681</v>
+        <v>0.007882534526288509</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -3013,7 +3013,7 @@
         <v>294</v>
       </c>
       <c r="G99">
-        <v>0.006838021799921989</v>
+        <v>0.006838015280663967</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -3039,7 +3039,7 @@
         <v>297</v>
       </c>
       <c r="G100">
-        <v>0.01181522756814957</v>
+        <v>0.01181522198021412</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -3065,7 +3065,7 @@
         <v>300</v>
       </c>
       <c r="G101">
-        <v>0.01340567227452993</v>
+        <v>0.01340568531304598</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -3091,7 +3091,7 @@
         <v>303</v>
       </c>
       <c r="G102">
-        <v>0.02357441559433937</v>
+        <v>0.02357440441846848</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -3117,7 +3117,7 @@
         <v>306</v>
       </c>
       <c r="G103">
-        <v>0.02981690317392349</v>
+        <v>0.02981689013540745</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -3143,7 +3143,7 @@
         <v>309</v>
       </c>
       <c r="G104">
-        <v>0.02478980273008347</v>
+        <v>0.02478979714214802</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -3195,7 +3195,7 @@
         <v>315</v>
       </c>
       <c r="G106">
-        <v>0.01386115886271</v>
+        <v>0.01386116538196802</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -3221,7 +3221,7 @@
         <v>318</v>
       </c>
       <c r="G107">
-        <v>0.01437486056238413</v>
+        <v>0.01437486708164215</v>
       </c>
       <c r="H107">
         <v>1</v>
@@ -3247,7 +3247,7 @@
         <v>321</v>
       </c>
       <c r="G108">
-        <v>0.01768604852259159</v>
+        <v>0.01768605783581734</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -3273,7 +3273,7 @@
         <v>324</v>
       </c>
       <c r="G109">
-        <v>0.007843589410185814</v>
+        <v>0.007843578234314919</v>
       </c>
       <c r="H109">
         <v>1</v>
@@ -3299,7 +3299,7 @@
         <v>327</v>
       </c>
       <c r="G110">
-        <v>0.01501929759979248</v>
+        <v>0.01501929108053446</v>
       </c>
       <c r="H110">
         <v>1</v>
@@ -3325,7 +3325,7 @@
         <v>330</v>
       </c>
       <c r="G111">
-        <v>0.02533987164497375</v>
+        <v>0.02533986046910286</v>
       </c>
       <c r="H111">
         <v>1</v>
@@ -3377,7 +3377,7 @@
         <v>336</v>
       </c>
       <c r="G113">
-        <v>0.01375426352024078</v>
+        <v>0.01375424955040216</v>
       </c>
       <c r="H113">
         <v>1</v>
@@ -3403,7 +3403,7 @@
         <v>339</v>
       </c>
       <c r="G114">
-        <v>0.0105744507163763</v>
+        <v>0.01057444699108601</v>
       </c>
       <c r="H114">
         <v>1</v>
@@ -3429,7 +3429,7 @@
         <v>342</v>
       </c>
       <c r="G115">
-        <v>0.01169091183692217</v>
+        <v>0.01169092301279306</v>
       </c>
       <c r="H115">
         <v>1</v>
@@ -3455,7 +3455,7 @@
         <v>345</v>
       </c>
       <c r="G116">
-        <v>0.01056243106722832</v>
+        <v>0.01056242547929287</v>
       </c>
       <c r="H116">
         <v>1</v>
@@ -3481,7 +3481,7 @@
         <v>348</v>
       </c>
       <c r="G117">
-        <v>0.0174174215644598</v>
+        <v>0.01741743832826614</v>
       </c>
       <c r="H117">
         <v>1</v>
@@ -3507,7 +3507,7 @@
         <v>351</v>
       </c>
       <c r="G118">
-        <v>0.01079575996845961</v>
+        <v>0.01079577580094337</v>
       </c>
       <c r="H118">
         <v>1</v>
@@ -3533,7 +3533,7 @@
         <v>354</v>
       </c>
       <c r="G119">
-        <v>0.01690835691988468</v>
+        <v>0.016908323392272</v>
       </c>
       <c r="H119">
         <v>1</v>
@@ -3559,7 +3559,7 @@
         <v>357</v>
       </c>
       <c r="G120">
-        <v>0.006712447851896286</v>
+        <v>0.006712441798299551</v>
       </c>
       <c r="H120">
         <v>1</v>
@@ -3585,7 +3585,7 @@
         <v>360</v>
       </c>
       <c r="G121">
-        <v>0.006645767949521542</v>
+        <v>0.00664576468989253</v>
       </c>
       <c r="H121">
         <v>1</v>
@@ -3637,7 +3637,7 @@
         <v>366</v>
       </c>
       <c r="G123">
-        <v>0.01011322904378176</v>
+        <v>0.01011322438716888</v>
       </c>
       <c r="H123">
         <v>1</v>
@@ -3663,7 +3663,7 @@
         <v>369</v>
       </c>
       <c r="G124">
-        <v>0.006725702900439501</v>
+        <v>0.006725696381181479</v>
       </c>
       <c r="H124">
         <v>1</v>
@@ -3689,7 +3689,7 @@
         <v>372</v>
       </c>
       <c r="G125">
-        <v>0.0102769872173667</v>
+        <v>0.01027698256075382</v>
       </c>
       <c r="H125">
         <v>1</v>
@@ -3715,7 +3715,7 @@
         <v>375</v>
       </c>
       <c r="G126">
-        <v>0.01253655925393105</v>
+        <v>0.01253656577318907</v>
       </c>
       <c r="H126">
         <v>1</v>
@@ -3741,7 +3741,7 @@
         <v>378</v>
       </c>
       <c r="G127">
-        <v>0.01632700860500336</v>
+        <v>0.01632702350616455</v>
       </c>
       <c r="H127">
         <v>1</v>
@@ -3767,7 +3767,7 @@
         <v>381</v>
       </c>
       <c r="G128">
-        <v>0.009403340518474579</v>
+        <v>0.009403335861861706</v>
       </c>
       <c r="H128">
         <v>1</v>
@@ -3793,7 +3793,7 @@
         <v>384</v>
       </c>
       <c r="G129">
-        <v>0.004202256444841623</v>
+        <v>0.004202258307486773</v>
       </c>
       <c r="H129">
         <v>1</v>
@@ -3819,7 +3819,7 @@
         <v>387</v>
       </c>
       <c r="G130">
-        <v>0.01013244036585093</v>
+        <v>0.01013242546468973</v>
       </c>
       <c r="H130">
         <v>1</v>
@@ -3871,7 +3871,7 @@
         <v>393</v>
       </c>
       <c r="G132">
-        <v>0.007158254273235798</v>
+        <v>0.007158247753977776</v>
       </c>
       <c r="H132">
         <v>1</v>
@@ -3897,7 +3897,7 @@
         <v>396</v>
       </c>
       <c r="G133">
-        <v>0.01338944025337696</v>
+        <v>0.01338944584131241</v>
       </c>
       <c r="H133">
         <v>1</v>
@@ -3923,7 +3923,7 @@
         <v>399</v>
       </c>
       <c r="G134">
-        <v>0.01067913044244051</v>
+        <v>0.01067914068698883</v>
       </c>
       <c r="H134">
         <v>1</v>
@@ -3949,7 +3949,7 @@
         <v>402</v>
       </c>
       <c r="G135">
-        <v>0.01188735477626324</v>
+        <v>0.01188733708113432</v>
       </c>
       <c r="H135">
         <v>1</v>
@@ -3975,7 +3975,7 @@
         <v>405</v>
       </c>
       <c r="G136">
-        <v>0.004185567144304514</v>
+        <v>0.0041855713352561</v>
       </c>
       <c r="H136">
         <v>1</v>
@@ -4027,7 +4027,7 @@
         <v>411</v>
       </c>
       <c r="G138">
-        <v>0.009550267830491066</v>
+        <v>0.009550272487103939</v>
       </c>
       <c r="H138">
         <v>1</v>
@@ -4053,7 +4053,7 @@
         <v>414</v>
       </c>
       <c r="G139">
-        <v>0.005476347636431456</v>
+        <v>0.005476350430399179</v>
       </c>
       <c r="H139">
         <v>1</v>
@@ -4079,7 +4079,7 @@
         <v>3</v>
       </c>
       <c r="G140">
-        <v>0.07866242527961731</v>
+        <v>0.07866236567497253</v>
       </c>
       <c r="H140">
         <v>1</v>
@@ -4105,7 +4105,7 @@
         <v>6</v>
       </c>
       <c r="G141">
-        <v>0.05640752986073494</v>
+        <v>0.05640751495957375</v>
       </c>
       <c r="H141">
         <v>1</v>
@@ -4157,7 +4157,7 @@
         <v>12</v>
       </c>
       <c r="G143">
-        <v>0.09869208931922913</v>
+        <v>0.09869211167097092</v>
       </c>
       <c r="H143">
         <v>1</v>
@@ -4183,7 +4183,7 @@
         <v>15</v>
       </c>
       <c r="G144">
-        <v>0.02938753925263882</v>
+        <v>0.02938752621412277</v>
       </c>
       <c r="H144">
         <v>1</v>
@@ -4209,7 +4209,7 @@
         <v>18</v>
       </c>
       <c r="G145">
-        <v>0.07606298476457596</v>
+        <v>0.07606296986341476</v>
       </c>
       <c r="H145">
         <v>1</v>
@@ -4235,7 +4235,7 @@
         <v>21</v>
       </c>
       <c r="G146">
-        <v>0.1267493963241577</v>
+        <v>0.1267493367195129</v>
       </c>
       <c r="H146">
         <v>1</v>
@@ -4287,7 +4287,7 @@
         <v>27</v>
       </c>
       <c r="G148">
-        <v>0.03953311592340469</v>
+        <v>0.03953306004405022</v>
       </c>
       <c r="H148">
         <v>1</v>
@@ -4313,7 +4313,7 @@
         <v>30</v>
       </c>
       <c r="G149">
-        <v>0.05565114691853523</v>
+        <v>0.05565112084150314</v>
       </c>
       <c r="H149">
         <v>1</v>
@@ -4365,7 +4365,7 @@
         <v>36</v>
       </c>
       <c r="G151">
-        <v>0.136856883764267</v>
+        <v>0.1368568688631058</v>
       </c>
       <c r="H151">
         <v>1</v>
@@ -4391,7 +4391,7 @@
         <v>39</v>
       </c>
       <c r="G152">
-        <v>0.03232687339186668</v>
+        <v>0.03232685104012489</v>
       </c>
       <c r="H152">
         <v>1</v>
@@ -4417,7 +4417,7 @@
         <v>42</v>
       </c>
       <c r="G153">
-        <v>0.09007839858531952</v>
+        <v>0.09007831662893295</v>
       </c>
       <c r="H153">
         <v>1</v>
@@ -4443,7 +4443,7 @@
         <v>45</v>
       </c>
       <c r="G154">
-        <v>0.06071194261312485</v>
+        <v>0.06071191281080246</v>
       </c>
       <c r="H154">
         <v>1</v>
@@ -4469,7 +4469,7 @@
         <v>48</v>
       </c>
       <c r="G155">
-        <v>0.05277770012617111</v>
+        <v>0.05277767777442932</v>
       </c>
       <c r="H155">
         <v>1</v>
@@ -4495,7 +4495,7 @@
         <v>51</v>
       </c>
       <c r="G156">
-        <v>0.1223277300596237</v>
+        <v>0.1223276555538177</v>
       </c>
       <c r="H156">
         <v>1</v>
@@ -4547,7 +4547,7 @@
         <v>57</v>
       </c>
       <c r="G158">
-        <v>0.1727525144815445</v>
+        <v>0.172752633690834</v>
       </c>
       <c r="H158">
         <v>1</v>
@@ -4573,7 +4573,7 @@
         <v>60</v>
       </c>
       <c r="G159">
-        <v>0.1568286865949631</v>
+        <v>0.1568287760019302</v>
       </c>
       <c r="H159">
         <v>1</v>
@@ -4625,7 +4625,7 @@
         <v>66</v>
       </c>
       <c r="G161">
-        <v>0.07428950816392899</v>
+        <v>0.07428954541683197</v>
       </c>
       <c r="H161">
         <v>1</v>
@@ -4677,7 +4677,7 @@
         <v>72</v>
       </c>
       <c r="G163">
-        <v>0.08990302681922913</v>
+        <v>0.08990299701690674</v>
       </c>
       <c r="H163">
         <v>1</v>
@@ -4703,7 +4703,7 @@
         <v>75</v>
       </c>
       <c r="G164">
-        <v>0.1155385226011276</v>
+        <v>0.1155384927988052</v>
       </c>
       <c r="H164">
         <v>1</v>
@@ -4729,7 +4729,7 @@
         <v>78</v>
       </c>
       <c r="G165">
-        <v>0.08212970197200775</v>
+        <v>0.08212972432374954</v>
       </c>
       <c r="H165">
         <v>1</v>
@@ -4755,7 +4755,7 @@
         <v>81</v>
       </c>
       <c r="G166">
-        <v>0.05027934163808823</v>
+        <v>0.05027936398983002</v>
       </c>
       <c r="H166">
         <v>1</v>
@@ -4833,7 +4833,7 @@
         <v>90</v>
       </c>
       <c r="G169">
-        <v>0.02439345605671406</v>
+        <v>0.02439343743026257</v>
       </c>
       <c r="H169">
         <v>1</v>
@@ -4885,7 +4885,7 @@
         <v>96</v>
       </c>
       <c r="G171">
-        <v>0.03240511938929558</v>
+        <v>0.03240512683987617</v>
       </c>
       <c r="H171">
         <v>1</v>
@@ -4963,7 +4963,7 @@
         <v>105</v>
       </c>
       <c r="G174">
-        <v>0.02095846645534039</v>
+        <v>0.02095846086740494</v>
       </c>
       <c r="H174">
         <v>1</v>
@@ -5041,7 +5041,7 @@
         <v>114</v>
       </c>
       <c r="G177">
-        <v>0.05525189638137817</v>
+        <v>0.05525192245841026</v>
       </c>
       <c r="H177">
         <v>1</v>
@@ -5067,7 +5067,7 @@
         <v>117</v>
       </c>
       <c r="G178">
-        <v>0.08541721105575562</v>
+        <v>0.0854172483086586</v>
       </c>
       <c r="H178">
         <v>1</v>
@@ -5093,7 +5093,7 @@
         <v>120</v>
       </c>
       <c r="G179">
-        <v>0.02998591773211956</v>
+        <v>0.02998592518270016</v>
       </c>
       <c r="H179">
         <v>1</v>
@@ -5119,7 +5119,7 @@
         <v>123</v>
       </c>
       <c r="G180">
-        <v>0.05142117291688919</v>
+        <v>0.05142119899392128</v>
       </c>
       <c r="H180">
         <v>1</v>
@@ -5145,7 +5145,7 @@
         <v>126</v>
       </c>
       <c r="G181">
-        <v>0.03603935614228249</v>
+        <v>0.03603936359286308</v>
       </c>
       <c r="H181">
         <v>1</v>
@@ -5171,7 +5171,7 @@
         <v>129</v>
       </c>
       <c r="G182">
-        <v>0.03681978955864906</v>
+        <v>0.03681978210806847</v>
       </c>
       <c r="H182">
         <v>1</v>
@@ -5197,7 +5197,7 @@
         <v>132</v>
       </c>
       <c r="G183">
-        <v>0.07143382728099823</v>
+        <v>0.07143387198448181</v>
       </c>
       <c r="H183">
         <v>1</v>
@@ -5223,7 +5223,7 @@
         <v>135</v>
       </c>
       <c r="G184">
-        <v>0.03722379356622696</v>
+        <v>0.03722381219267845</v>
       </c>
       <c r="H184">
         <v>0</v>
@@ -5249,7 +5249,7 @@
         <v>138</v>
       </c>
       <c r="G185">
-        <v>0.07884225249290466</v>
+        <v>0.07884227484464645</v>
       </c>
       <c r="H185">
         <v>0</v>
@@ -5353,7 +5353,7 @@
         <v>150</v>
       </c>
       <c r="G189">
-        <v>0.09348233044147491</v>
+        <v>0.09348230808973312</v>
       </c>
       <c r="H189">
         <v>0</v>
@@ -5379,7 +5379,7 @@
         <v>153</v>
       </c>
       <c r="G190">
-        <v>0.1222047209739685</v>
+        <v>0.1222047880291939</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -5405,7 +5405,7 @@
         <v>156</v>
       </c>
       <c r="G191">
-        <v>0.03144156560301781</v>
+        <v>0.03144155442714691</v>
       </c>
       <c r="H191">
         <v>0</v>
@@ -5431,7 +5431,7 @@
         <v>159</v>
       </c>
       <c r="G192">
-        <v>0.06695117801427841</v>
+        <v>0.0669512078166008</v>
       </c>
       <c r="H192">
         <v>0</v>
@@ -5457,7 +5457,7 @@
         <v>162</v>
       </c>
       <c r="G193">
-        <v>0.0593736432492733</v>
+        <v>0.05937354266643524</v>
       </c>
       <c r="H193">
         <v>0</v>
@@ -5483,7 +5483,7 @@
         <v>165</v>
       </c>
       <c r="G194">
-        <v>0.03563129156827927</v>
+        <v>0.03563127294182777</v>
       </c>
       <c r="H194">
         <v>0</v>
@@ -5509,7 +5509,7 @@
         <v>168</v>
       </c>
       <c r="G195">
-        <v>0.02907131426036358</v>
+        <v>0.02907132171094418</v>
       </c>
       <c r="H195">
         <v>0</v>
@@ -5535,7 +5535,7 @@
         <v>171</v>
       </c>
       <c r="G196">
-        <v>0.02159416675567627</v>
+        <v>0.02159417979419231</v>
       </c>
       <c r="H196">
         <v>0</v>
@@ -5561,7 +5561,7 @@
         <v>174</v>
       </c>
       <c r="G197">
-        <v>0.04592843353748322</v>
+        <v>0.04592842981219292</v>
       </c>
       <c r="H197">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>180</v>
       </c>
       <c r="G199">
-        <v>0.02464843355119228</v>
+        <v>0.02464845590293407</v>
       </c>
       <c r="H199">
         <v>0</v>
@@ -5639,7 +5639,7 @@
         <v>183</v>
       </c>
       <c r="G200">
-        <v>0.04804056510329247</v>
+        <v>0.04804052785038948</v>
       </c>
       <c r="H200">
         <v>0</v>
@@ -5665,7 +5665,7 @@
         <v>186</v>
       </c>
       <c r="G201">
-        <v>0.04706104099750519</v>
+        <v>0.04706097766757011</v>
       </c>
       <c r="H201">
         <v>0</v>
@@ -5691,7 +5691,7 @@
         <v>189</v>
       </c>
       <c r="G202">
-        <v>0.03469990566372871</v>
+        <v>0.03469989821314812</v>
       </c>
       <c r="H202">
         <v>0</v>
@@ -5717,7 +5717,7 @@
         <v>192</v>
       </c>
       <c r="G203">
-        <v>0.0790613517165184</v>
+        <v>0.07906129956245422</v>
       </c>
       <c r="H203">
         <v>0</v>
@@ -5743,7 +5743,7 @@
         <v>195</v>
       </c>
       <c r="G204">
-        <v>0.05777019262313843</v>
+        <v>0.05777022987604141</v>
       </c>
       <c r="H204">
         <v>0</v>
@@ -5769,7 +5769,7 @@
         <v>198</v>
       </c>
       <c r="G205">
-        <v>0.06241723150014877</v>
+        <v>0.06241721287369728</v>
       </c>
       <c r="H205">
         <v>1</v>
@@ -5795,7 +5795,7 @@
         <v>201</v>
       </c>
       <c r="G206">
-        <v>0.04723959788680077</v>
+        <v>0.04723955318331718</v>
       </c>
       <c r="H206">
         <v>1</v>
@@ -5821,7 +5821,7 @@
         <v>204</v>
       </c>
       <c r="G207">
-        <v>0.05555568635463715</v>
+        <v>0.05555569753050804</v>
       </c>
       <c r="H207">
         <v>1</v>
@@ -5847,7 +5847,7 @@
         <v>207</v>
       </c>
       <c r="G208">
-        <v>0.08136860281229019</v>
+        <v>0.08136862516403198</v>
       </c>
       <c r="H208">
         <v>1</v>
@@ -5899,7 +5899,7 @@
         <v>213</v>
       </c>
       <c r="G210">
-        <v>0.0947510302066803</v>
+        <v>0.09475104510784149</v>
       </c>
       <c r="H210">
         <v>1</v>
@@ -5925,7 +5925,7 @@
         <v>216</v>
       </c>
       <c r="G211">
-        <v>0.05588633567094803</v>
+        <v>0.05588638782501221</v>
       </c>
       <c r="H211">
         <v>1</v>
@@ -5951,7 +5951,7 @@
         <v>219</v>
       </c>
       <c r="G212">
-        <v>0.05541704967617989</v>
+        <v>0.05541707947850227</v>
       </c>
       <c r="H212">
         <v>1</v>
@@ -5977,7 +5977,7 @@
         <v>222</v>
       </c>
       <c r="G213">
-        <v>0.1098063439130783</v>
+        <v>0.1098062694072723</v>
       </c>
       <c r="H213">
         <v>1</v>
@@ -6003,7 +6003,7 @@
         <v>225</v>
       </c>
       <c r="G214">
-        <v>0.04527938365936279</v>
+        <v>0.04527942463755608</v>
       </c>
       <c r="H214">
         <v>1</v>
@@ -6029,7 +6029,7 @@
         <v>228</v>
       </c>
       <c r="G215">
-        <v>0.04196200519800186</v>
+        <v>0.04196196049451828</v>
       </c>
       <c r="H215">
         <v>1</v>
@@ -6055,7 +6055,7 @@
         <v>231</v>
       </c>
       <c r="G216">
-        <v>0.04288831725716591</v>
+        <v>0.0428883470594883</v>
       </c>
       <c r="H216">
         <v>1</v>
@@ -6081,7 +6081,7 @@
         <v>234</v>
       </c>
       <c r="G217">
-        <v>0.04322343692183495</v>
+        <v>0.04322341084480286</v>
       </c>
       <c r="H217">
         <v>1</v>
@@ -6107,7 +6107,7 @@
         <v>237</v>
       </c>
       <c r="G218">
-        <v>0.05568153783679008</v>
+        <v>0.0556815080344677</v>
       </c>
       <c r="H218">
         <v>1</v>
@@ -6133,7 +6133,7 @@
         <v>240</v>
       </c>
       <c r="G219">
-        <v>0.03061085939407349</v>
+        <v>0.03061086684465408</v>
       </c>
       <c r="H219">
         <v>1</v>
@@ -6159,7 +6159,7 @@
         <v>243</v>
       </c>
       <c r="G220">
-        <v>0.05495242774486542</v>
+        <v>0.05495244264602661</v>
       </c>
       <c r="H220">
         <v>1</v>
@@ -6185,7 +6185,7 @@
         <v>246</v>
       </c>
       <c r="G221">
-        <v>0.0291754025965929</v>
+        <v>0.02917541563510895</v>
       </c>
       <c r="H221">
         <v>1</v>
@@ -6237,7 +6237,7 @@
         <v>252</v>
       </c>
       <c r="G223">
-        <v>0.01214520912617445</v>
+        <v>0.01214519795030355</v>
       </c>
       <c r="H223">
         <v>1</v>
@@ -6263,7 +6263,7 @@
         <v>255</v>
       </c>
       <c r="G224">
-        <v>0.06401153653860092</v>
+        <v>0.06401155889034271</v>
       </c>
       <c r="H224">
         <v>1</v>
@@ -6289,7 +6289,7 @@
         <v>258</v>
       </c>
       <c r="G225">
-        <v>0.05997253954410553</v>
+        <v>0.05997250974178314</v>
       </c>
       <c r="H225">
         <v>1</v>
@@ -6315,7 +6315,7 @@
         <v>261</v>
       </c>
       <c r="G226">
-        <v>0.05257409065961838</v>
+        <v>0.05257410556077957</v>
       </c>
       <c r="H226">
         <v>1</v>
@@ -6341,7 +6341,7 @@
         <v>264</v>
       </c>
       <c r="G227">
-        <v>0.1122054010629654</v>
+        <v>0.1122053787112236</v>
       </c>
       <c r="H227">
         <v>1</v>
@@ -6393,7 +6393,7 @@
         <v>270</v>
       </c>
       <c r="G229">
-        <v>0.03144871816039085</v>
+        <v>0.03144869580864906</v>
       </c>
       <c r="H229">
         <v>1</v>
@@ -6419,7 +6419,7 @@
         <v>273</v>
       </c>
       <c r="G230">
-        <v>0.03503848612308502</v>
+        <v>0.03503847494721413</v>
       </c>
       <c r="H230">
         <v>0</v>
@@ -6445,7 +6445,7 @@
         <v>276</v>
       </c>
       <c r="G231">
-        <v>0.06009431183338165</v>
+        <v>0.06009435281157494</v>
       </c>
       <c r="H231">
         <v>0</v>
@@ -6471,7 +6471,7 @@
         <v>279</v>
       </c>
       <c r="G232">
-        <v>0.03701450303196907</v>
+        <v>0.03701448440551758</v>
       </c>
       <c r="H232">
         <v>0</v>
@@ -6497,7 +6497,7 @@
         <v>282</v>
       </c>
       <c r="G233">
-        <v>0.02436059713363647</v>
+        <v>0.02436059154570103</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -6523,7 +6523,7 @@
         <v>285</v>
       </c>
       <c r="G234">
-        <v>0.06460327655076981</v>
+        <v>0.06460330635309219</v>
       </c>
       <c r="H234">
         <v>0</v>
@@ -6549,7 +6549,7 @@
         <v>288</v>
       </c>
       <c r="G235">
-        <v>0.1298256665468216</v>
+        <v>0.1298257261514664</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>291</v>
       </c>
       <c r="G236">
-        <v>0.07554347068071365</v>
+        <v>0.07554350793361664</v>
       </c>
       <c r="H236">
         <v>0</v>
@@ -6601,7 +6601,7 @@
         <v>294</v>
       </c>
       <c r="G237">
-        <v>0.02617214992642403</v>
+        <v>0.02617216855287552</v>
       </c>
       <c r="H237">
         <v>0</v>
@@ -6627,7 +6627,7 @@
         <v>297</v>
       </c>
       <c r="G238">
-        <v>0.0592174120247364</v>
+        <v>0.0592174269258976</v>
       </c>
       <c r="H238">
         <v>0</v>
@@ -6679,7 +6679,7 @@
         <v>303</v>
       </c>
       <c r="G240">
-        <v>0.1183758229017258</v>
+        <v>0.1183757930994034</v>
       </c>
       <c r="H240">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         <v>306</v>
       </c>
       <c r="G241">
-        <v>0.05354449525475502</v>
+        <v>0.05354451015591621</v>
       </c>
       <c r="H241">
         <v>0</v>
@@ -6731,7 +6731,7 @@
         <v>309</v>
       </c>
       <c r="G242">
-        <v>0.1341041177511215</v>
+        <v>0.1341039836406708</v>
       </c>
       <c r="H242">
         <v>0</v>
@@ -6757,7 +6757,7 @@
         <v>312</v>
       </c>
       <c r="G243">
-        <v>0.1382820010185242</v>
+        <v>0.1382819414138794</v>
       </c>
       <c r="H243">
         <v>0</v>
@@ -6783,7 +6783,7 @@
         <v>315</v>
       </c>
       <c r="G244">
-        <v>0.03905033692717552</v>
+        <v>0.03905034065246582</v>
       </c>
       <c r="H244">
         <v>0</v>
@@ -6809,7 +6809,7 @@
         <v>318</v>
       </c>
       <c r="G245">
-        <v>0.09223373979330063</v>
+        <v>0.09223376214504242</v>
       </c>
       <c r="H245">
         <v>0</v>
@@ -6835,7 +6835,7 @@
         <v>321</v>
       </c>
       <c r="G246">
-        <v>0.06200546398758888</v>
+        <v>0.06200549378991127</v>
       </c>
       <c r="H246">
         <v>0</v>
@@ -6861,7 +6861,7 @@
         <v>324</v>
       </c>
       <c r="G247">
-        <v>0.06244624778628349</v>
+        <v>0.06244621798396111</v>
       </c>
       <c r="H247">
         <v>0</v>
@@ -6887,7 +6887,7 @@
         <v>327</v>
       </c>
       <c r="G248">
-        <v>0.05026581510901451</v>
+        <v>0.05026574432849884</v>
       </c>
       <c r="H248">
         <v>0</v>
@@ -6913,7 +6913,7 @@
         <v>330</v>
       </c>
       <c r="G249">
-        <v>0.02480059862136841</v>
+        <v>0.02480057999491692</v>
       </c>
       <c r="H249">
         <v>0</v>
@@ -6939,7 +6939,7 @@
         <v>333</v>
       </c>
       <c r="G250">
-        <v>0.04400543496012688</v>
+        <v>0.04400546848773956</v>
       </c>
       <c r="H250">
         <v>0</v>
@@ -6965,7 +6965,7 @@
         <v>336</v>
       </c>
       <c r="G251">
-        <v>0.05112103372812271</v>
+        <v>0.0511210598051548</v>
       </c>
       <c r="H251">
         <v>0</v>
@@ -6991,7 +6991,7 @@
         <v>339</v>
       </c>
       <c r="G252">
-        <v>0.08199631422758102</v>
+        <v>0.08199633657932281</v>
       </c>
       <c r="H252">
         <v>0</v>
@@ -7017,7 +7017,7 @@
         <v>342</v>
       </c>
       <c r="G253">
-        <v>0.06128640100359917</v>
+        <v>0.06128641590476036</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>348</v>
       </c>
       <c r="G255">
-        <v>0.06041547283530235</v>
+        <v>0.06041548401117325</v>
       </c>
       <c r="H255">
         <v>0</v>
@@ -7095,7 +7095,7 @@
         <v>351</v>
       </c>
       <c r="G256">
-        <v>0.05319324880838394</v>
+        <v>0.05319323763251305</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -7121,7 +7121,7 @@
         <v>354</v>
       </c>
       <c r="G257">
-        <v>0.08175884187221527</v>
+        <v>0.08175881952047348</v>
       </c>
       <c r="H257">
         <v>0</v>
@@ -7147,7 +7147,7 @@
         <v>357</v>
       </c>
       <c r="G258">
-        <v>0.06564829498529434</v>
+        <v>0.06564828008413315</v>
       </c>
       <c r="H258">
         <v>0</v>
@@ -7173,7 +7173,7 @@
         <v>360</v>
       </c>
       <c r="G259">
-        <v>0.0393933579325676</v>
+        <v>0.03939337655901909</v>
       </c>
       <c r="H259">
         <v>0</v>
@@ -7199,7 +7199,7 @@
         <v>363</v>
       </c>
       <c r="G260">
-        <v>0.03125574067234993</v>
+        <v>0.03125570714473724</v>
       </c>
       <c r="H260">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>366</v>
       </c>
       <c r="G261">
-        <v>0.06955331563949585</v>
+        <v>0.06955336779356003</v>
       </c>
       <c r="H261">
         <v>0</v>
@@ -7251,7 +7251,7 @@
         <v>369</v>
       </c>
       <c r="G262">
-        <v>0.03342085331678391</v>
+        <v>0.03342088311910629</v>
       </c>
       <c r="H262">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>372</v>
       </c>
       <c r="G263">
-        <v>0.05520032346248627</v>
+        <v>0.05520034953951836</v>
       </c>
       <c r="H263">
         <v>0</v>
@@ -7303,7 +7303,7 @@
         <v>375</v>
       </c>
       <c r="G264">
-        <v>0.07415908575057983</v>
+        <v>0.07415906339883804</v>
       </c>
       <c r="H264">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>378</v>
       </c>
       <c r="G265">
-        <v>0.0668206661939621</v>
+        <v>0.06682072579860687</v>
       </c>
       <c r="H265">
         <v>0</v>
@@ -7355,7 +7355,7 @@
         <v>381</v>
       </c>
       <c r="G266">
-        <v>0.05591819435358047</v>
+        <v>0.05591816827654839</v>
       </c>
       <c r="H266">
         <v>0</v>
@@ -7381,7 +7381,7 @@
         <v>384</v>
       </c>
       <c r="G267">
-        <v>0.03349239006638527</v>
+        <v>0.03349236398935318</v>
       </c>
       <c r="H267">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>387</v>
       </c>
       <c r="G268">
-        <v>0.04747173190116882</v>
+        <v>0.04747170954942703</v>
       </c>
       <c r="H268">
         <v>0</v>
@@ -7433,7 +7433,7 @@
         <v>390</v>
       </c>
       <c r="G269">
-        <v>0.02904710732400417</v>
+        <v>0.02904708683490753</v>
       </c>
       <c r="H269">
         <v>0</v>
@@ -7459,7 +7459,7 @@
         <v>393</v>
       </c>
       <c r="G270">
-        <v>0.06619373708963394</v>
+        <v>0.06619370728731155</v>
       </c>
       <c r="H270">
         <v>0</v>
@@ -7485,7 +7485,7 @@
         <v>396</v>
       </c>
       <c r="G271">
-        <v>0.05879266932606697</v>
+        <v>0.05879265442490578</v>
       </c>
       <c r="H271">
         <v>0</v>
@@ -7511,7 +7511,7 @@
         <v>399</v>
       </c>
       <c r="G272">
-        <v>0.02786096185445786</v>
+        <v>0.02786094136536121</v>
       </c>
       <c r="H272">
         <v>0</v>
@@ -7537,7 +7537,7 @@
         <v>402</v>
       </c>
       <c r="G273">
-        <v>0.0230963584035635</v>
+        <v>0.02309634536504745</v>
       </c>
       <c r="H273">
         <v>0</v>
@@ -7563,7 +7563,7 @@
         <v>405</v>
       </c>
       <c r="G274">
-        <v>0.06558748334646225</v>
+        <v>0.06558745354413986</v>
       </c>
       <c r="H274">
         <v>0</v>
@@ -7615,7 +7615,7 @@
         <v>411</v>
       </c>
       <c r="G276">
-        <v>0.04371687769889832</v>
+        <v>0.04371689632534981</v>
       </c>
       <c r="H276">
         <v>0</v>
@@ -7641,7 +7641,7 @@
         <v>414</v>
       </c>
       <c r="G277">
-        <v>0.05927976220846176</v>
+        <v>0.05927973613142967</v>
       </c>
       <c r="H277">
         <v>0</v>
@@ -7747,7 +7747,7 @@
         <v>69</v>
       </c>
       <c r="I3">
-        <v>0.05992241203784943</v>
+        <v>0.05992240458726883</v>
       </c>
       <c r="J3">
         <v>0.5356017643352238</v>
@@ -7803,7 +7803,7 @@
         <v>21</v>
       </c>
       <c r="F2">
-        <v>0.01864773035049438</v>
+        <v>0.01864773407578468</v>
       </c>
       <c r="G2">
         <v>0.2720588235294117</v>
@@ -7826,7 +7826,7 @@
         <v>21</v>
       </c>
       <c r="F3">
-        <v>0.05992239713668823</v>
+        <v>0.05992238968610764</v>
       </c>
       <c r="G3">
         <v>0.5356017643352238</v>
